--- a/TestData/GlobalTransfer_TestData.xlsx
+++ b/TestData/GlobalTransfer_TestData.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26.35" customWidth="1" style="4" min="1" max="1"/>
@@ -531,6 +531,11 @@
           <t>Address</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>PayoutAccount</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="13.8" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
@@ -699,6 +704,67 @@
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>123 Main Street</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>USDT payout to a saved account</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USDT-TRC 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Personal bank payout to a saved account</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SAVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Global Transfer state checks</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12345678</t>
         </is>
       </c>
     </row>
